--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -10906,11 +10906,7 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djursåsen, Hjd</t>
@@ -11028,11 +11024,7 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djursåsen, Hjd</t>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>136944271</v>
       </c>
       <c r="B94" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850825</v>
+        <v>6850824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92431</v>
+        <v>92432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>437511</v>
       </c>
       <c r="R7" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>437511</v>
       </c>
       <c r="R90" t="n">
-        <v>6850824</v>
+        <v>6850825</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80654</v>
+        <v>80655</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 36995-2026 artfynd.xlsx
+++ b/artfynd/A 36995-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944171</v>
       </c>
       <c r="B2" t="n">
-        <v>92432</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136944213</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136944226</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136944233</v>
       </c>
       <c r="B5" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136944248</v>
       </c>
       <c r="B6" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136944265</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136944251</v>
       </c>
       <c r="B8" t="n">
-        <v>81505</v>
+        <v>81508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136944257</v>
       </c>
       <c r="B9" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136944206</v>
       </c>
       <c r="B10" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136944269</v>
       </c>
       <c r="B11" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136944187</v>
       </c>
       <c r="B12" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136944162</v>
       </c>
       <c r="B13" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>136944166</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136944215</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136944219</v>
       </c>
       <c r="B16" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>136944247</v>
       </c>
       <c r="B17" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>136944158</v>
       </c>
       <c r="B18" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>136944160</v>
       </c>
       <c r="B19" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>136944161</v>
       </c>
       <c r="B20" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>136944163</v>
       </c>
       <c r="B21" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136944164</v>
       </c>
       <c r="B22" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136944165</v>
       </c>
       <c r="B23" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136944168</v>
       </c>
       <c r="B24" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136944169</v>
       </c>
       <c r="B25" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136944172</v>
       </c>
       <c r="B26" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136944173</v>
       </c>
       <c r="B27" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136944175</v>
       </c>
       <c r="B28" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136944176</v>
       </c>
       <c r="B29" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136944178</v>
       </c>
       <c r="B30" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136944180</v>
       </c>
       <c r="B31" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136944181</v>
       </c>
       <c r="B32" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>136944183</v>
       </c>
       <c r="B33" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136944188</v>
       </c>
       <c r="B34" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>136944190</v>
       </c>
       <c r="B35" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>136944192</v>
       </c>
       <c r="B36" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>136944193</v>
       </c>
       <c r="B37" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>136944194</v>
       </c>
       <c r="B38" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>136944196</v>
       </c>
       <c r="B39" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>136944199</v>
       </c>
       <c r="B40" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>136944200</v>
       </c>
       <c r="B41" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136944202</v>
       </c>
       <c r="B42" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>136944204</v>
       </c>
       <c r="B43" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>136944205</v>
       </c>
       <c r="B44" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>136944207</v>
       </c>
       <c r="B45" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>136944208</v>
       </c>
       <c r="B46" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>136944209</v>
       </c>
       <c r="B47" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>136944210</v>
       </c>
       <c r="B48" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136944214</v>
       </c>
       <c r="B49" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>136944216</v>
       </c>
       <c r="B50" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>136944222</v>
       </c>
       <c r="B51" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>136944223</v>
       </c>
       <c r="B52" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>136944224</v>
       </c>
       <c r="B53" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>136944225</v>
       </c>
       <c r="B54" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>136944227</v>
       </c>
       <c r="B55" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>136944228</v>
       </c>
       <c r="B56" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>136944230</v>
       </c>
       <c r="B57" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>136944231</v>
       </c>
       <c r="B58" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>136944234</v>
       </c>
       <c r="B59" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>136944239</v>
       </c>
       <c r="B60" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>136944240</v>
       </c>
       <c r="B61" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>136944243</v>
       </c>
       <c r="B62" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>136944246</v>
       </c>
       <c r="B63" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>136944250</v>
       </c>
       <c r="B64" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>136944253</v>
       </c>
       <c r="B65" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>136944255</v>
       </c>
       <c r="B66" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>136944260</v>
       </c>
       <c r="B67" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>136944261</v>
       </c>
       <c r="B68" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>136944262</v>
       </c>
       <c r="B69" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>136944256</v>
       </c>
       <c r="B70" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136944235</v>
       </c>
       <c r="B71" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>136944252</v>
       </c>
       <c r="B72" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136944157</v>
       </c>
       <c r="B73" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136944221</v>
       </c>
       <c r="B74" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>136944245</v>
       </c>
       <c r="B75" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>136944259</v>
       </c>
       <c r="B76" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136944159</v>
       </c>
       <c r="B77" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>136944170</v>
       </c>
       <c r="B78" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>136944182</v>
       </c>
       <c r="B79" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>136944185</v>
       </c>
       <c r="B80" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>136944191</v>
       </c>
       <c r="B81" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136944201</v>
       </c>
       <c r="B82" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>136944211</v>
       </c>
       <c r="B83" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>136944218</v>
       </c>
       <c r="B84" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>136944220</v>
       </c>
       <c r="B85" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>136944232</v>
       </c>
       <c r="B86" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>136944237</v>
       </c>
       <c r="B87" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>136944242</v>
       </c>
       <c r="B88" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>136944244</v>
       </c>
       <c r="B89" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>136944263</v>
       </c>
       <c r="B90" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>136944267</v>
       </c>
       <c r="B91" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>136944195</v>
       </c>
       <c r="B92" t="n">
-        <v>80655</v>
+        <v>80658</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>136944238</v>
       </c>
       <c r="B93" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>136944273</v>
       </c>
       <c r="B95" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>136944177</v>
       </c>
       <c r="B96" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>136944258</v>
       </c>
       <c r="B97" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>136944197</v>
       </c>
       <c r="B98" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>136944249</v>
       </c>
       <c r="B99" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>136944268</v>
       </c>
       <c r="B100" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>136944266</v>
       </c>
       <c r="B101" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
